--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/178.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/178.xlsx
@@ -426,13 +426,13 @@
         <v>-7.02408166718314</v>
       </c>
       <c r="E2">
-        <v>-14.98876196690366</v>
+        <v>-13.24871394335235</v>
       </c>
       <c r="F2">
-        <v>1.59703928236516</v>
+        <v>0.8689811663311686</v>
       </c>
       <c r="G2">
-        <v>-10.05799136007926</v>
+        <v>-10.75794331399291</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.677273170845572</v>
       </c>
       <c r="E3">
-        <v>-15.12246516198012</v>
+        <v>-13.66188738333819</v>
       </c>
       <c r="F3">
-        <v>1.956850931529341</v>
+        <v>0.9546168962967259</v>
       </c>
       <c r="G3">
-        <v>-9.909030052994211</v>
+        <v>-10.28545563353704</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.270166291964308</v>
       </c>
       <c r="E4">
-        <v>-16.72684463273563</v>
+        <v>-13.17058870977202</v>
       </c>
       <c r="F4">
-        <v>1.710731946328643</v>
+        <v>1.20444967186913</v>
       </c>
       <c r="G4">
-        <v>-10.08048982756415</v>
+        <v>-9.206525668469787</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.844395949915111</v>
       </c>
       <c r="E5">
-        <v>-15.90550171654244</v>
+        <v>-15.56966102718559</v>
       </c>
       <c r="F5">
-        <v>2.102049840974576</v>
+        <v>1.299750759036614</v>
       </c>
       <c r="G5">
-        <v>-9.002225282150285</v>
+        <v>-9.349130728119434</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.390932616498408</v>
       </c>
       <c r="E6">
-        <v>-17.97429883915458</v>
+        <v>-16.66840014719264</v>
       </c>
       <c r="F6">
-        <v>2.023163865620622</v>
+        <v>1.025465564129825</v>
       </c>
       <c r="G6">
-        <v>-8.595567799742829</v>
+        <v>-9.380405451828928</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.927899922392334</v>
       </c>
       <c r="E7">
-        <v>-17.85274101136668</v>
+        <v>-17.34250878797445</v>
       </c>
       <c r="F7">
-        <v>2.176042165049823</v>
+        <v>1.105643843510778</v>
       </c>
       <c r="G7">
-        <v>-8.065724917819093</v>
+        <v>-8.565908622256499</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.45828887698047</v>
       </c>
       <c r="E8">
-        <v>-18.97406815972399</v>
+        <v>-17.9458554939124</v>
       </c>
       <c r="F8">
-        <v>2.115905684028756</v>
+        <v>1.187920533229688</v>
       </c>
       <c r="G8">
-        <v>-7.586675736104396</v>
+        <v>-8.732965371259201</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.00050318742396</v>
       </c>
       <c r="E9">
-        <v>-19.24863859575706</v>
+        <v>-17.20288234889595</v>
       </c>
       <c r="F9">
-        <v>2.37756240796583</v>
+        <v>1.376003031453192</v>
       </c>
       <c r="G9">
-        <v>-7.506593639509425</v>
+        <v>-7.861447705318365</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.563910761415543</v>
       </c>
       <c r="E10">
-        <v>-19.57080329361075</v>
+        <v>-19.03886609429975</v>
       </c>
       <c r="F10">
-        <v>2.418133786107558</v>
+        <v>1.547556391037255</v>
       </c>
       <c r="G10">
-        <v>-6.440561559863172</v>
+        <v>-7.788132363805666</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.16339055217075</v>
       </c>
       <c r="E11">
-        <v>-21.35220081332609</v>
+        <v>-19.06360061932964</v>
       </c>
       <c r="F11">
-        <v>2.487633136500703</v>
+        <v>1.834801051450085</v>
       </c>
       <c r="G11">
-        <v>-6.349730121902188</v>
+        <v>-7.079808040223202</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.810495482277814</v>
       </c>
       <c r="E12">
-        <v>-21.15023087258399</v>
+        <v>-20.45101637190366</v>
       </c>
       <c r="F12">
-        <v>2.720583607014522</v>
+        <v>1.592915312161356</v>
       </c>
       <c r="G12">
-        <v>-6.127522994760767</v>
+        <v>-6.994750193682708</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.510122420682964</v>
       </c>
       <c r="E13">
-        <v>-21.41356616460403</v>
+        <v>-20.85836166584162</v>
       </c>
       <c r="F13">
-        <v>2.870052187607782</v>
+        <v>1.971761522723203</v>
       </c>
       <c r="G13">
-        <v>-4.873213569205082</v>
+        <v>-6.76721308822306</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.271484950043711</v>
       </c>
       <c r="E14">
-        <v>-23.5601352998239</v>
+        <v>-22.67642623959707</v>
       </c>
       <c r="F14">
-        <v>2.865983647111018</v>
+        <v>2.432859083709314</v>
       </c>
       <c r="G14">
-        <v>-5.701177698031266</v>
+        <v>-5.433821350825264</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.090669256824314</v>
       </c>
       <c r="E15">
-        <v>-23.74961118077884</v>
+        <v>-22.73854331756029</v>
       </c>
       <c r="F15">
-        <v>3.576332763598566</v>
+        <v>2.231886803040048</v>
       </c>
       <c r="G15">
-        <v>-5.190002982403481</v>
+        <v>-4.988519870337897</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.965593571627966</v>
       </c>
       <c r="E16">
-        <v>-24.85181458340176</v>
+        <v>-23.64121309845723</v>
       </c>
       <c r="F16">
-        <v>4.060503336066714</v>
+        <v>3.3040398707334</v>
       </c>
       <c r="G16">
-        <v>-4.89624834506733</v>
+        <v>-4.908662890839597</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.885046131837664</v>
       </c>
       <c r="E17">
-        <v>-26.26912732137441</v>
+        <v>-24.45630219204584</v>
       </c>
       <c r="F17">
-        <v>4.060726638600791</v>
+        <v>2.868599929283324</v>
       </c>
       <c r="G17">
-        <v>-4.506219732903634</v>
+        <v>-5.433285042447903</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.839339963728446</v>
       </c>
       <c r="E18">
-        <v>-27.17657011387544</v>
+        <v>-25.34907725723602</v>
       </c>
       <c r="F18">
-        <v>4.380581387518434</v>
+        <v>3.28338834559607</v>
       </c>
       <c r="G18">
-        <v>-4.508719194785785</v>
+        <v>-5.398034353545743</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.820034500842705</v>
       </c>
       <c r="E19">
-        <v>-28.54507495899342</v>
+        <v>-26.47708843322865</v>
       </c>
       <c r="F19">
-        <v>4.615528911191622</v>
+        <v>3.482130768336396</v>
       </c>
       <c r="G19">
-        <v>-3.794482236870183</v>
+        <v>-4.756165921118609</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.822991199422815</v>
       </c>
       <c r="E20">
-        <v>-28.39448055586834</v>
+        <v>-26.88069773611029</v>
       </c>
       <c r="F20">
-        <v>4.788051498795934</v>
+        <v>3.666287259595526</v>
       </c>
       <c r="G20">
-        <v>-4.281953446436787</v>
+        <v>-3.843071113750066</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.850928505135228</v>
       </c>
       <c r="E21">
-        <v>-28.77596826322251</v>
+        <v>-26.15635473316139</v>
       </c>
       <c r="F21">
-        <v>5.286627460270919</v>
+        <v>4.010660943496004</v>
       </c>
       <c r="G21">
-        <v>-4.131783790229907</v>
+        <v>-5.075640186749357</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.907677745904247</v>
       </c>
       <c r="E22">
-        <v>-30.12737585472453</v>
+        <v>-27.91642766877462</v>
       </c>
       <c r="F22">
-        <v>5.040072955943475</v>
+        <v>4.199696832680602</v>
       </c>
       <c r="G22">
-        <v>-3.909675979454663</v>
+        <v>-3.65935901013929</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.001011470298051</v>
       </c>
       <c r="E23">
-        <v>-29.96649502289103</v>
+        <v>-28.01745792388574</v>
       </c>
       <c r="F23">
-        <v>5.335742931826442</v>
+        <v>4.748059757019257</v>
       </c>
       <c r="G23">
-        <v>-3.918422440769418</v>
+        <v>-4.45831944949592</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.134862967773131</v>
       </c>
       <c r="E24">
-        <v>-30.80152978024642</v>
+        <v>-28.8980513939953</v>
       </c>
       <c r="F24">
-        <v>5.025471187403124</v>
+        <v>3.691279722647076</v>
       </c>
       <c r="G24">
-        <v>-3.901336715241239</v>
+        <v>-3.824356599816566</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.314287214259372</v>
       </c>
       <c r="E25">
-        <v>-29.89489079188175</v>
+        <v>-30.64049498029666</v>
       </c>
       <c r="F25">
-        <v>5.014838185886862</v>
+        <v>3.960318099856014</v>
       </c>
       <c r="G25">
-        <v>-3.710404311809313</v>
+        <v>-5.294811543631267</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.535160731482673</v>
       </c>
       <c r="E26">
-        <v>-30.93562921679856</v>
+        <v>-28.78205000381481</v>
       </c>
       <c r="F26">
-        <v>5.144467682477413</v>
+        <v>4.059068498507325</v>
       </c>
       <c r="G26">
-        <v>-3.898135417704764</v>
+        <v>-4.543552754949996</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.793789186665563</v>
       </c>
       <c r="E27">
-        <v>-31.47992009320248</v>
+        <v>-28.82728493067743</v>
       </c>
       <c r="F27">
-        <v>4.757029867324306</v>
+        <v>3.646850436895338</v>
       </c>
       <c r="G27">
-        <v>-3.813915139185705</v>
+        <v>-4.339887993374033</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.0793094234389</v>
       </c>
       <c r="E28">
-        <v>-30.41358446895732</v>
+        <v>-29.08101985780121</v>
       </c>
       <c r="F28">
-        <v>4.929888200582691</v>
+        <v>3.675342890020009</v>
       </c>
       <c r="G28">
-        <v>-3.194763670249051</v>
+        <v>-4.934855927146311</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.378829884555941</v>
       </c>
       <c r="E29">
-        <v>-30.90493521997457</v>
+        <v>-28.16967804917957</v>
       </c>
       <c r="F29">
-        <v>4.509300253207606</v>
+        <v>4.087461178159324</v>
       </c>
       <c r="G29">
-        <v>-4.200523957807333</v>
+        <v>-4.654081938869643</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.679722277146888</v>
       </c>
       <c r="E30">
-        <v>-29.72006678857863</v>
+        <v>-28.66748866836877</v>
       </c>
       <c r="F30">
-        <v>4.685322830885039</v>
+        <v>3.85690843840148</v>
       </c>
       <c r="G30">
-        <v>-3.305021389434478</v>
+        <v>-4.856899200787553</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.966218604523574</v>
       </c>
       <c r="E31">
-        <v>-29.6431778284024</v>
+        <v>-28.97947335665321</v>
       </c>
       <c r="F31">
-        <v>4.560739021341079</v>
+        <v>4.196477158554513</v>
       </c>
       <c r="G31">
-        <v>-3.220890495644979</v>
+        <v>-4.75775498297746</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.230385383982244</v>
       </c>
       <c r="E32">
-        <v>-28.6469022255299</v>
+        <v>-27.10637423828254</v>
       </c>
       <c r="F32">
-        <v>4.496941012243517</v>
+        <v>4.104299139452276</v>
       </c>
       <c r="G32">
-        <v>-3.642849319534945</v>
+        <v>-4.188281560403109</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.461622116628247</v>
       </c>
       <c r="E33">
-        <v>-29.00912580445544</v>
+        <v>-28.32565680789977</v>
       </c>
       <c r="F33">
-        <v>4.123778722212181</v>
+        <v>3.344749031289771</v>
       </c>
       <c r="G33">
-        <v>-3.689445248000187</v>
+        <v>-4.382855563928233</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.659990501227629</v>
       </c>
       <c r="E34">
-        <v>-29.04211573760131</v>
+        <v>-26.72940594798803</v>
       </c>
       <c r="F34">
-        <v>4.09268899138619</v>
+        <v>3.484262436498578</v>
       </c>
       <c r="G34">
-        <v>-4.235883894712289</v>
+        <v>-4.959774403420405</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.82557856596148</v>
       </c>
       <c r="E35">
-        <v>-27.70853448403049</v>
+        <v>-27.03351561997313</v>
       </c>
       <c r="F35">
-        <v>4.397154869923508</v>
+        <v>3.383215664269879</v>
       </c>
       <c r="G35">
-        <v>-3.463046970206048</v>
+        <v>-4.458074469126014</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.962458328321292</v>
       </c>
       <c r="E36">
-        <v>-27.4967694540098</v>
+        <v>-27.21205070772554</v>
       </c>
       <c r="F36">
-        <v>4.435490055312635</v>
+        <v>3.784978099428136</v>
       </c>
       <c r="G36">
-        <v>-3.783325698402839</v>
+        <v>-4.799070591307564</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.078698124800201</v>
       </c>
       <c r="E37">
-        <v>-27.28918420549819</v>
+        <v>-26.74549561613729</v>
       </c>
       <c r="F37">
-        <v>4.340272904558669</v>
+        <v>3.298270430083454</v>
       </c>
       <c r="G37">
-        <v>-3.743231681376726</v>
+        <v>-4.417179300079397</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.17907000174407</v>
       </c>
       <c r="E38">
-        <v>-25.92911137898249</v>
+        <v>-26.19862350954899</v>
       </c>
       <c r="F38">
-        <v>4.170296916066384</v>
+        <v>3.589056256923206</v>
       </c>
       <c r="G38">
-        <v>-2.923831933860636</v>
+        <v>-4.741606141836895</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.274021253930844</v>
       </c>
       <c r="E39">
-        <v>-25.96048917538164</v>
+        <v>-25.53815010400428</v>
       </c>
       <c r="F39">
-        <v>4.2023226170884</v>
+        <v>3.242321267502809</v>
       </c>
       <c r="G39">
-        <v>-2.774003263844301</v>
+        <v>-3.457670644250272</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.36610432231864</v>
       </c>
       <c r="E40">
-        <v>-25.15290829169775</v>
+        <v>-23.95466501232016</v>
       </c>
       <c r="F40">
-        <v>4.280188685832812</v>
+        <v>3.960940496280782</v>
       </c>
       <c r="G40">
-        <v>-2.703654171134788</v>
+        <v>-4.050837641249187</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.462280094465959</v>
       </c>
       <c r="E41">
-        <v>-23.84959535839419</v>
+        <v>-25.09894699542235</v>
       </c>
       <c r="F41">
-        <v>4.424724022499477</v>
+        <v>3.457763869121445</v>
       </c>
       <c r="G41">
-        <v>-3.527774756589878</v>
+        <v>-4.907484336627617</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.565386765014031</v>
       </c>
       <c r="E42">
-        <v>-24.53543727532988</v>
+        <v>-23.41555923865502</v>
       </c>
       <c r="F42">
-        <v>4.227069605723058</v>
+        <v>3.47812557607625</v>
       </c>
       <c r="G42">
-        <v>-3.200236002025466</v>
+        <v>-4.220373988860803</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.675239468846547</v>
       </c>
       <c r="E43">
-        <v>-23.59525361575339</v>
+        <v>-22.89631082351351</v>
       </c>
       <c r="F43">
-        <v>4.411319535631198</v>
+        <v>3.724936640761995</v>
       </c>
       <c r="G43">
-        <v>-3.13044639151209</v>
+        <v>-5.206439841005962</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.794454367717157</v>
       </c>
       <c r="E44">
-        <v>-23.61440000385782</v>
+        <v>-23.24154809643628</v>
       </c>
       <c r="F44">
-        <v>4.227275487492064</v>
+        <v>3.486509715192587</v>
       </c>
       <c r="G44">
-        <v>-2.832292039154248</v>
+        <v>-4.905935001315238</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.91916942892574</v>
       </c>
       <c r="E45">
-        <v>-22.43115955886764</v>
+        <v>-21.84993897693116</v>
       </c>
       <c r="F45">
-        <v>4.149939960229325</v>
+        <v>3.436974561569472</v>
       </c>
       <c r="G45">
-        <v>-4.008538800893919</v>
+        <v>-5.029259443744168</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.051640075977513</v>
       </c>
       <c r="E46">
-        <v>-22.16716763811649</v>
+        <v>-21.46870033564742</v>
       </c>
       <c r="F46">
-        <v>4.168578595148133</v>
+        <v>3.608141496910167</v>
       </c>
       <c r="G46">
-        <v>-4.034178976095574</v>
+        <v>-4.757903957526727</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.187824803631178</v>
       </c>
       <c r="E47">
-        <v>-21.62292657492664</v>
+        <v>-21.91197001388823</v>
       </c>
       <c r="F47">
-        <v>4.332349623863726</v>
+        <v>3.323196377486555</v>
       </c>
       <c r="G47">
-        <v>-3.973135826896953</v>
+        <v>-5.144436633600952</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.32837819091334</v>
       </c>
       <c r="E48">
-        <v>-21.01612917179485</v>
+        <v>-20.41129259790837</v>
       </c>
       <c r="F48">
-        <v>4.419765439278237</v>
+        <v>3.383093718914391</v>
       </c>
       <c r="G48">
-        <v>-4.249652453610118</v>
+        <v>-4.775482954340257</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.473121553442401</v>
       </c>
       <c r="E49">
-        <v>-20.3652606596204</v>
+        <v>-19.9291369133637</v>
       </c>
       <c r="F49">
-        <v>3.85953739022111</v>
+        <v>3.15556110633729</v>
       </c>
       <c r="G49">
-        <v>-4.349101241609825</v>
+        <v>-4.371447423999905</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.618450449054687</v>
       </c>
       <c r="E50">
-        <v>-19.06683847824513</v>
+        <v>-18.6374938575779</v>
       </c>
       <c r="F50">
-        <v>4.198583487422048</v>
+        <v>2.898487627319497</v>
       </c>
       <c r="G50">
-        <v>-4.593849873328143</v>
+        <v>-5.200100146298258</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.766134185832577</v>
       </c>
       <c r="E51">
-        <v>-19.6667118446192</v>
+        <v>-19.66898966704506</v>
       </c>
       <c r="F51">
-        <v>4.054599280413956</v>
+        <v>2.979131516239589</v>
       </c>
       <c r="G51">
-        <v>-4.349124415428599</v>
+        <v>-4.828822464068995</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.911070715840858</v>
       </c>
       <c r="E52">
-        <v>-18.60928146451012</v>
+        <v>-18.78862714910989</v>
       </c>
       <c r="F52">
-        <v>4.02955297136128</v>
+        <v>3.503843376437072</v>
       </c>
       <c r="G52">
-        <v>-4.536299349673452</v>
+        <v>-4.429411765847004</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.054276389349321</v>
       </c>
       <c r="E53">
-        <v>-19.31792424807442</v>
+        <v>-18.93232468632129</v>
       </c>
       <c r="F53">
-        <v>4.002891282274858</v>
+        <v>3.502999261184142</v>
       </c>
       <c r="G53">
-        <v>-4.784494259298153</v>
+        <v>-4.719074568896615</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.192618559881533</v>
       </c>
       <c r="E54">
-        <v>-17.00841608958456</v>
+        <v>-17.79275231618707</v>
       </c>
       <c r="F54">
-        <v>3.849322487066525</v>
+        <v>3.36362997321364</v>
       </c>
       <c r="G54">
-        <v>-4.937514295214346</v>
+        <v>-5.543665251818283</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.326270476078662</v>
       </c>
       <c r="E55">
-        <v>-17.62953252752861</v>
+        <v>-16.84932626922109</v>
       </c>
       <c r="F55">
-        <v>3.831746518816978</v>
+        <v>2.900980380430399</v>
       </c>
       <c r="G55">
-        <v>-5.414792335065534</v>
+        <v>-5.241779914637682</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.456961607570619</v>
       </c>
       <c r="E56">
-        <v>-16.76424077109098</v>
+        <v>-16.1203189380443</v>
       </c>
       <c r="F56">
-        <v>3.841882236675791</v>
+        <v>3.558129647806505</v>
       </c>
       <c r="G56">
-        <v>-4.941427360041764</v>
+        <v>-5.400437809607253</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.582702333297004</v>
       </c>
       <c r="E57">
-        <v>-17.11428728340988</v>
+        <v>-17.10066563359481</v>
       </c>
       <c r="F57">
-        <v>4.25088379157352</v>
+        <v>3.08559139528726</v>
       </c>
       <c r="G57">
-        <v>-5.016662817967242</v>
+        <v>-5.569047204467875</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.70969582283625</v>
       </c>
       <c r="E58">
-        <v>-16.67639743229018</v>
+        <v>-16.33832420524755</v>
       </c>
       <c r="F58">
-        <v>3.808499299684243</v>
+        <v>3.719724664594284</v>
       </c>
       <c r="G58">
-        <v>-6.121795750977828</v>
+        <v>-5.87559047922223</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.836895368825518</v>
       </c>
       <c r="E59">
-        <v>-15.67616167889798</v>
+        <v>-14.96998238519385</v>
       </c>
       <c r="F59">
-        <v>3.866626057898616</v>
+        <v>3.348694042725131</v>
       </c>
       <c r="G59">
-        <v>-5.833738562514763</v>
+        <v>-6.535123982646914</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.970354582553289</v>
       </c>
       <c r="E60">
-        <v>-16.2591211948534</v>
+        <v>-14.78028008053853</v>
       </c>
       <c r="F60">
-        <v>3.308306374469594</v>
+        <v>3.290114344618941</v>
       </c>
       <c r="G60">
-        <v>-5.570881246696631</v>
+        <v>-7.107653038754012</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.112081559430553</v>
       </c>
       <c r="E61">
-        <v>-15.04306289872963</v>
+        <v>-15.30953189476298</v>
       </c>
       <c r="F61">
-        <v>3.938101873274229</v>
+        <v>3.147099365631097</v>
       </c>
       <c r="G61">
-        <v>-6.249711920069727</v>
+        <v>-6.567977836578641</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.264869534015839</v>
       </c>
       <c r="E62">
-        <v>-15.82428353521487</v>
+        <v>-14.42650663411131</v>
       </c>
       <c r="F62">
-        <v>3.791935319514661</v>
+        <v>3.281068216429951</v>
       </c>
       <c r="G62">
-        <v>-6.479344600855733</v>
+        <v>-6.786659232720739</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.432789976655471</v>
       </c>
       <c r="E63">
-        <v>-14.85773057149171</v>
+        <v>-13.24028645322408</v>
       </c>
       <c r="F63">
-        <v>3.750971182305904</v>
+        <v>3.410038891359677</v>
       </c>
       <c r="G63">
-        <v>-6.302266830505658</v>
+        <v>-6.782981216626609</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.612404400885858</v>
       </c>
       <c r="E64">
-        <v>-14.44915806109767</v>
+        <v>-13.98459096959879</v>
       </c>
       <c r="F64">
-        <v>3.425923461691535</v>
+        <v>3.146210906612535</v>
       </c>
       <c r="G64">
-        <v>-6.774195028765383</v>
+        <v>-6.950832496558736</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.807869780024292</v>
       </c>
       <c r="E65">
-        <v>-14.65202011121928</v>
+        <v>-13.41018574104385</v>
       </c>
       <c r="F65">
-        <v>3.923365489731065</v>
+        <v>3.228129678794556</v>
       </c>
       <c r="G65">
-        <v>-6.073230047916719</v>
+        <v>-6.891063907392734</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.01265355739716</v>
       </c>
       <c r="E66">
-        <v>-14.79627465073362</v>
+        <v>-14.10277055577696</v>
       </c>
       <c r="F66">
-        <v>3.244193207894858</v>
+        <v>3.348415310484013</v>
       </c>
       <c r="G66">
-        <v>-7.175496048490297</v>
+        <v>-7.080675403154491</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.226681897236425</v>
       </c>
       <c r="E67">
-        <v>-14.42181966351337</v>
+        <v>-12.8717230106878</v>
       </c>
       <c r="F67">
-        <v>3.553947080483829</v>
+        <v>2.94098795926623</v>
       </c>
       <c r="G67">
-        <v>-7.247265365236156</v>
+        <v>-7.461609946721809</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.446602518691547</v>
       </c>
       <c r="E68">
-        <v>-12.7038162514314</v>
+        <v>-12.97180228625732</v>
       </c>
       <c r="F68">
-        <v>3.475319249194091</v>
+        <v>2.83730590039424</v>
       </c>
       <c r="G68">
-        <v>-7.124146176630661</v>
+        <v>-7.753659653105235</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.668163005141356</v>
       </c>
       <c r="E69">
-        <v>-13.63515580127091</v>
+        <v>-12.90131205985392</v>
       </c>
       <c r="F69">
-        <v>3.106630928373872</v>
+        <v>2.957608952848767</v>
       </c>
       <c r="G69">
-        <v>-6.942423710888987</v>
+        <v>-7.981312627658757</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.890844777787139</v>
       </c>
       <c r="E70">
-        <v>-14.04999119121756</v>
+        <v>-13.59254738933274</v>
       </c>
       <c r="F70">
-        <v>3.230804558085733</v>
+        <v>2.746418601613086</v>
       </c>
       <c r="G70">
-        <v>-7.722944411591876</v>
+        <v>-7.522437910460377</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.10568759731095</v>
       </c>
       <c r="E71">
-        <v>-13.98089120633452</v>
+        <v>-13.99915454200745</v>
       </c>
       <c r="F71">
-        <v>3.04259694709491</v>
+        <v>2.807587658891019</v>
       </c>
       <c r="G71">
-        <v>-7.097963071960566</v>
+        <v>-7.939503748043301</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.31204562015605</v>
       </c>
       <c r="E72">
-        <v>-14.06086405730998</v>
+        <v>-13.1283606896505</v>
       </c>
       <c r="F72">
-        <v>3.387531262889452</v>
+        <v>2.141005839082556</v>
       </c>
       <c r="G72">
-        <v>-7.770185896437276</v>
+        <v>-7.440601224729594</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.499618782345</v>
       </c>
       <c r="E73">
-        <v>-13.01037582785465</v>
+        <v>-12.87501068281737</v>
       </c>
       <c r="F73">
-        <v>3.156683953831336</v>
+        <v>2.548840202720607</v>
       </c>
       <c r="G73">
-        <v>-7.531856412519605</v>
+        <v>-7.362700777645004</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.66291422168774</v>
       </c>
       <c r="E74">
-        <v>-14.39870180370421</v>
+        <v>-13.8692371512014</v>
       </c>
       <c r="F74">
-        <v>2.907701628335523</v>
+        <v>2.413864114959533</v>
       </c>
       <c r="G74">
-        <v>-7.881873771295668</v>
+        <v>-8.359880131165495</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.79593871189689</v>
       </c>
       <c r="E75">
-        <v>-13.55211717339226</v>
+        <v>-13.77321538834276</v>
       </c>
       <c r="F75">
-        <v>3.115613708326245</v>
+        <v>2.503872456957619</v>
       </c>
       <c r="G75">
-        <v>-6.933938782671835</v>
+        <v>-7.7499981897388</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.88867565329214</v>
       </c>
       <c r="E76">
-        <v>-14.01677030589729</v>
+        <v>-15.25448829319975</v>
       </c>
       <c r="F76">
-        <v>2.708566446528168</v>
+        <v>2.157251494363134</v>
       </c>
       <c r="G76">
-        <v>-6.144045927547269</v>
+        <v>-8.333183891936812</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.93777279975794</v>
       </c>
       <c r="E77">
-        <v>-16.3211114755444</v>
+        <v>-14.66352696367277</v>
       </c>
       <c r="F77">
-        <v>2.820640563046071</v>
+        <v>2.614475310680079</v>
       </c>
       <c r="G77">
-        <v>-6.587543160715734</v>
+        <v>-8.651330628806313</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.93277506614231</v>
       </c>
       <c r="E78">
-        <v>-14.77419381147222</v>
+        <v>-15.31013871028001</v>
       </c>
       <c r="F78">
-        <v>2.922616970647133</v>
+        <v>2.503029925410605</v>
       </c>
       <c r="G78">
-        <v>-6.008068580067245</v>
+        <v>-7.847136216952096</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.87180659583268</v>
       </c>
       <c r="E79">
-        <v>-15.43742958616161</v>
+        <v>-14.95910499062742</v>
       </c>
       <c r="F79">
-        <v>2.8234848988702</v>
+        <v>2.554576385546328</v>
       </c>
       <c r="G79">
-        <v>-6.965011563103435</v>
+        <v>-7.425419062886497</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.75104027822397</v>
       </c>
       <c r="E80">
-        <v>-16.75462229229868</v>
+        <v>-14.1211561602481</v>
       </c>
       <c r="F80">
-        <v>2.505955030236422</v>
+        <v>2.700866468367301</v>
       </c>
       <c r="G80">
-        <v>-6.548776672450868</v>
+        <v>-7.296923548325225</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.5697082041482</v>
       </c>
       <c r="E81">
-        <v>-16.23806831919174</v>
+        <v>-16.54182477020424</v>
       </c>
       <c r="F81">
-        <v>2.50846995523014</v>
+        <v>2.190795969358057</v>
       </c>
       <c r="G81">
-        <v>-5.81940058978418</v>
+        <v>-8.187940327492369</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.33582550064346</v>
       </c>
       <c r="E82">
-        <v>-16.82571027727109</v>
+        <v>-16.2709314550654</v>
       </c>
       <c r="F82">
-        <v>2.53960878093951</v>
+        <v>2.2331537677724</v>
       </c>
       <c r="G82">
-        <v>-6.046762236330246</v>
+        <v>-8.199494131424425</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.05254160983509</v>
       </c>
       <c r="E83">
-        <v>-17.32981094685694</v>
+        <v>-18.46894858348642</v>
       </c>
       <c r="F83">
-        <v>2.847930983380924</v>
+        <v>2.008340378252108</v>
       </c>
       <c r="G83">
-        <v>-6.005522770547545</v>
+        <v>-6.973791129873582</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.734675713920653</v>
       </c>
       <c r="E84">
-        <v>-18.09534947785361</v>
+        <v>-18.0384265595772</v>
       </c>
       <c r="F84">
-        <v>2.768265824716573</v>
+        <v>2.074388833455511</v>
       </c>
       <c r="G84">
-        <v>-5.954977361253952</v>
+        <v>-7.101747025511952</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.39147724853107</v>
       </c>
       <c r="E85">
-        <v>-19.76399705172598</v>
+        <v>-18.96895098409533</v>
       </c>
       <c r="F85">
-        <v>2.341865676631825</v>
+        <v>2.179900072659833</v>
       </c>
       <c r="G85">
-        <v>-5.834847595270419</v>
+        <v>-7.027825854165566</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.038369347655282</v>
       </c>
       <c r="E86">
-        <v>-20.70643589135829</v>
+        <v>-19.04369344759192</v>
       </c>
       <c r="F86">
-        <v>2.594978307155104</v>
+        <v>2.062515790207461</v>
       </c>
       <c r="G86">
-        <v>-5.341278360820477</v>
+        <v>-5.489736464983554</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.690139856352792</v>
       </c>
       <c r="E87">
-        <v>-21.23794741411256</v>
+        <v>-20.9650298710923</v>
       </c>
       <c r="F87">
-        <v>2.341735812746759</v>
+        <v>1.775111175497172</v>
       </c>
       <c r="G87">
-        <v>-4.900949319733096</v>
+        <v>-6.470505444265879</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.359046606195934</v>
       </c>
       <c r="E88">
-        <v>-22.24884772379284</v>
+        <v>-22.55448349151852</v>
       </c>
       <c r="F88">
-        <v>2.843152942634043</v>
+        <v>2.160168680659373</v>
       </c>
       <c r="G88">
-        <v>-4.190214918998043</v>
+        <v>-5.793094994929131</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.063465419230528</v>
       </c>
       <c r="E89">
-        <v>-24.91793483238775</v>
+        <v>-24.955865330676</v>
       </c>
       <c r="F89">
-        <v>2.32849444758777</v>
+        <v>1.696526104267151</v>
       </c>
       <c r="G89">
-        <v>-4.216537066580788</v>
+        <v>-5.509447453124375</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.810908838230359</v>
       </c>
       <c r="E90">
-        <v>-25.48807423842746</v>
+        <v>-23.81150183504167</v>
       </c>
       <c r="F90">
-        <v>2.279393229385485</v>
+        <v>1.862455724145488</v>
       </c>
       <c r="G90">
-        <v>-4.031682824758963</v>
+        <v>-5.685767108545959</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.616045158017652</v>
       </c>
       <c r="E91">
-        <v>-27.63438525062889</v>
+        <v>-28.18473975372909</v>
       </c>
       <c r="F91">
-        <v>2.214930063803438</v>
+        <v>1.675375711766457</v>
       </c>
       <c r="G91">
-        <v>-4.292375043794412</v>
+        <v>-5.662282098490369</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.482844229045279</v>
       </c>
       <c r="E92">
-        <v>-28.75082164705792</v>
+        <v>-29.1514466855685</v>
       </c>
       <c r="F92">
-        <v>2.247717527370781</v>
+        <v>1.547185803853042</v>
       </c>
       <c r="G92">
-        <v>-4.082625499517269</v>
+        <v>-4.88639616154246</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.416628484220496</v>
       </c>
       <c r="E93">
-        <v>-31.2301973940495</v>
+        <v>-30.08070540160148</v>
       </c>
       <c r="F93">
-        <v>1.767758028931787</v>
+        <v>1.336302691564956</v>
       </c>
       <c r="G93">
-        <v>-3.996564557678375</v>
+        <v>-6.033132720345066</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.415953420209404</v>
       </c>
       <c r="E94">
-        <v>-32.90166394299164</v>
+        <v>-32.14909949002694</v>
       </c>
       <c r="F94">
-        <v>1.613060051405746</v>
+        <v>1.012985961516162</v>
       </c>
       <c r="G94">
-        <v>-4.227965069782353</v>
+        <v>-5.497585768457166</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.475240679725789</v>
       </c>
       <c r="E95">
-        <v>-35.08750174056902</v>
+        <v>-33.67606469762133</v>
       </c>
       <c r="F95">
-        <v>1.700068854399989</v>
+        <v>1.066163638744788</v>
       </c>
       <c r="G95">
-        <v>-4.518117833571775</v>
+        <v>-5.987251869716308</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.593720146674538</v>
       </c>
       <c r="E96">
-        <v>-37.88000335129498</v>
+        <v>-38.13295485241544</v>
       </c>
       <c r="F96">
-        <v>1.483701368526736</v>
+        <v>0.5756962515568528</v>
       </c>
       <c r="G96">
-        <v>-4.279781728563025</v>
+        <v>-5.247437636964297</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.756742293648721</v>
       </c>
       <c r="E97">
-        <v>-39.03218752154056</v>
+        <v>-38.1723729544152</v>
       </c>
       <c r="F97">
-        <v>1.331293429754421</v>
+        <v>1.018871012697935</v>
       </c>
       <c r="G97">
-        <v>-4.906295850779019</v>
+        <v>-6.294324831756946</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.971067605849855</v>
       </c>
       <c r="E98">
-        <v>-41.58089420558957</v>
+        <v>-39.56670595103593</v>
       </c>
       <c r="F98">
-        <v>1.232516108102548</v>
+        <v>0.4188927370162354</v>
       </c>
       <c r="G98">
-        <v>-5.020135580237937</v>
+        <v>-6.41576557377403</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.216351578365943</v>
       </c>
       <c r="E99">
-        <v>-44.08407161196547</v>
+        <v>-41.86170487880521</v>
       </c>
       <c r="F99">
-        <v>1.035309880100197</v>
+        <v>0.313449597166277</v>
       </c>
       <c r="G99">
-        <v>-5.356152641928423</v>
+        <v>-6.192340165874158</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.510080271876241</v>
       </c>
       <c r="E100">
-        <v>-45.95692392850273</v>
+        <v>-45.4468773725448</v>
       </c>
       <c r="F100">
-        <v>0.7475140900287939</v>
+        <v>0.3686496668489189</v>
       </c>
       <c r="G100">
-        <v>-4.812279668009256</v>
+        <v>-5.37347010564435</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.815885922895088</v>
       </c>
       <c r="E101">
-        <v>-47.50635489564916</v>
+        <v>-47.72568926997367</v>
       </c>
       <c r="F101">
-        <v>0.9202172201074655</v>
+        <v>-0.420902958028629</v>
       </c>
       <c r="G101">
-        <v>-5.050129122823733</v>
+        <v>-5.393012255962669</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.18301806328015</v>
       </c>
       <c r="E102">
-        <v>-50.37168908595898</v>
+        <v>-48.85368912478128</v>
       </c>
       <c r="F102">
-        <v>0.335071142176814</v>
+        <v>-0.2456096769252561</v>
       </c>
       <c r="G102">
-        <v>-4.926337893473766</v>
+        <v>-7.107232599470525</v>
       </c>
     </row>
   </sheetData>
